--- a/data/trans_camb/IP04F-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Provincia-trans_camb.xlsx
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 7,58</t>
+          <t>-12,97; 7,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 10,96</t>
+          <t>-8,22; 11,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 6,82</t>
+          <t>-7,93; 6,87</t>
         </is>
       </c>
     </row>
@@ -617,24 +617,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,21; 70,1</t>
+          <t>-58,6; 80,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 198,23</t>
+          <t>-51,72; 183,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,01; 69,17</t>
+          <t>-44,15; 70,24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 1,77</t>
+          <t>-8,84; 1,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 2,66</t>
+          <t>-7,02; 1,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 0,33</t>
+          <t>-5,95; 1,0</t>
         </is>
       </c>
     </row>
@@ -713,24 +713,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,48; 58,25</t>
+          <t>-81,21; 91,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,45; 107,73</t>
+          <t>-86,56; 76,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,46; 19,11</t>
+          <t>-71,84; 32,94</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 0,84</t>
+          <t>-15,69; 0,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 6,74</t>
+          <t>-9,58; 6,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 1,57</t>
+          <t>-10,23; 1,21</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-88,14; 17,45</t>
+          <t>-86,59; 39,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,17; 113,08</t>
+          <t>-67,65; 124,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,1; 24,67</t>
+          <t>-69,84; 20,28</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 6,56</t>
+          <t>-7,42; 7,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,53</t>
+          <t>-3,5; 5,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,42</t>
+          <t>-3,61; 4,61</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,26; 188,7</t>
+          <t>-67,24; 245,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 772,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,78; 172,6</t>
+          <t>-58,44; 179,7</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 8,71</t>
+          <t>-12,77; 8,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 5,2</t>
+          <t>-13,92; 5,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 4,12</t>
+          <t>-10,37; 4,18</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-77,8; 263,83</t>
+          <t>-80,76; 207,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-83,0; 115,75</t>
+          <t>-81,81; 141,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 76,57</t>
+          <t>-70,76; 77,45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 15,0</t>
+          <t>-6,7; 14,91</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 7,6</t>
+          <t>-8,8; 6,7</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 7,62</t>
+          <t>-5,21; 8,3</t>
         </is>
       </c>
     </row>
@@ -1097,24 +1097,24 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 223,62</t>
+          <t>-48,84; 224,03</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-80,94; 209,89</t>
+          <t>-76,37; 177,4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 110,85</t>
+          <t>-42,87; 123,9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 8,23</t>
+          <t>-4,53; 8,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 6,96</t>
+          <t>-5,0; 6,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 5,57</t>
+          <t>-3,08; 5,69</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 116,71</t>
+          <t>-35,94; 127,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 102,29</t>
+          <t>-43,2; 105,59</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,92; 68,32</t>
+          <t>-26,66; 75,98</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 2,12</t>
+          <t>-8,24; 2,59</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 2,29</t>
+          <t>-9,09; 2,22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 0,46</t>
+          <t>-6,93; 0,51</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 24,72</t>
+          <t>-58,28; 29,5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-55,45; 27,77</t>
+          <t>-57,3; 25,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 5,17</t>
+          <t>-48,42; 6,46</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,06</t>
+          <t>-4,06; 1,02</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,17</t>
+          <t>-3,59; 1,26</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,63</t>
+          <t>-3,11; 0,31</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 11,47</t>
+          <t>-34,4; 11,24</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 14,4</t>
+          <t>-35,94; 17,2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 7,46</t>
+          <t>-29,22; 3,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04F-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Provincia-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 7,07</t>
+          <t>-13,91; 7,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 11,07</t>
+          <t>-8,23; 11,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 6,87</t>
+          <t>-7,6; 6,92</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,6; 80,45</t>
+          <t>-64,17; 62,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,72; 183,96</t>
+          <t>-49,32; 163,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,15; 70,24</t>
+          <t>-42,16; 68,82</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 1,79</t>
+          <t>-8,36; 1,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 1,75</t>
+          <t>-6,92; 1,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 1,0</t>
+          <t>-6,06; 0,43</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,21; 91,61</t>
+          <t>-82,52; 71,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-86,56; 76,41</t>
+          <t>-85,98; 66,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,84; 32,94</t>
+          <t>-73,66; 17,73</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 0,84</t>
+          <t>-15,04; 1,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 6,89</t>
+          <t>-10,28; 6,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 1,21</t>
+          <t>-9,99; 1,44</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-86,59; 39,39</t>
+          <t>-85,77; 23,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,65; 124,09</t>
+          <t>-69,93; 114,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,84; 20,28</t>
+          <t>-68,53; 19,25</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 7,03</t>
+          <t>-6,35; 6,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 5,47</t>
+          <t>-3,55; 5,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 4,61</t>
+          <t>-3,68; 4,8</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,24; 245,8</t>
+          <t>-66,89; 206,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 772,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 179,7</t>
+          <t>-57,35; 159,17</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 8,53</t>
+          <t>-11,29; 8,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 5,86</t>
+          <t>-13,98; 4,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 4,18</t>
+          <t>-9,57; 4,21</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-80,76; 207,19</t>
+          <t>-77,98; 258,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-81,81; 141,85</t>
+          <t>-85,28; 123,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 77,45</t>
+          <t>-68,55; 80,64</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 14,91</t>
+          <t>-5,94; 15,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 6,7</t>
+          <t>-8,11; 8,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 8,3</t>
+          <t>-5,28; 8,19</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-48,84; 224,03</t>
+          <t>-37,42; 242,58</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,37; 177,4</t>
+          <t>-75,9; 245,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 123,9</t>
+          <t>-44,13; 124,44</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 8,57</t>
+          <t>-5,31; 7,32</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 6,73</t>
+          <t>-4,75; 7,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 5,69</t>
+          <t>-3,43; 4,97</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 127,53</t>
+          <t>-39,65; 104,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-43,2; 105,59</t>
+          <t>-39,84; 106,34</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-26,66; 75,98</t>
+          <t>-30,92; 63,47</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 2,59</t>
+          <t>-8,03; 2,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 2,22</t>
+          <t>-8,94; 1,94</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 0,51</t>
+          <t>-6,97; 0,39</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 29,5</t>
+          <t>-57,71; 29,78</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-57,3; 25,42</t>
+          <t>-56,75; 22,17</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 6,46</t>
+          <t>-50,48; 5,94</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,02</t>
+          <t>-4,24; 1,01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,26</t>
+          <t>-3,61; 1,13</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,31</t>
+          <t>-3,1; 0,44</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 11,24</t>
+          <t>-35,13; 11,42</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 17,2</t>
+          <t>-35,0; 14,91</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 3,48</t>
+          <t>-29,73; 5,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04F-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Provincia-trans_camb.xlsx
@@ -495,12 +495,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>-2,92</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 7,32</t>
+          <t>-7,03; 10,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 11,14</t>
+          <t>-12,72; 7,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 6,92</t>
+          <t>-7,94; 6,82</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>-17,61%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,17; 62,26</t>
+          <t>-47,71; 198,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,32; 163,53</t>
+          <t>-61,21; 70,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 68,82</t>
+          <t>-45,01; 69,17</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>-3,23</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,28</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,84</t>
+          <t>-6,92; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 1,49</t>
+          <t>-8,55; 1,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 0,43</t>
+          <t>-6,34; 0,33</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-41,81%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>-45,08%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-41,81%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,52; 71,13</t>
+          <t>-85,45; 107,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,98; 66,18</t>
+          <t>-83,48; 58,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,66; 17,73</t>
+          <t>-75,46; 19,11</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>-6,85</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 1,08</t>
+          <t>-9,46; 6,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 6,25</t>
+          <t>-15,3; 0,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 1,44</t>
+          <t>-9,93; 1,57</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-18,28%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>-54,53%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-18,28%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,77; 23,73</t>
+          <t>-67,17; 113,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,93; 114,65</t>
+          <t>-88,14; 17,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 19,25</t>
+          <t>-68,1; 24,67</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0,07</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 6,72</t>
+          <t>-3,75; 5,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 5,45</t>
+          <t>-7,23; 6,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 4,8</t>
+          <t>-3,63; 4,42</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>1,02%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34,4%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,89; 206,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,26; 188,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,35; 159,17</t>
+          <t>-58,78; 172,6</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-4,16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>-1,46</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-4,16</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 8,53</t>
+          <t>-14,4; 5,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 4,49</t>
+          <t>-12,08; 8,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 4,21</t>
+          <t>-9,89; 4,12</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-37,8%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>-15,24%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-37,8%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-77,98; 258,84</t>
+          <t>-83,0; 115,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-85,28; 123,05</t>
+          <t>-77,8; 263,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-68,55; 80,64</t>
+          <t>-68,77; 76,57</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,96</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>4,42</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 15,31</t>
+          <t>-8,9; 7,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 8,15</t>
+          <t>-5,7; 15,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 8,19</t>
+          <t>-5,45; 7,62</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-12,78%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>38,5%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-12,78%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 242,58</t>
+          <t>-80,94; 209,89</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-75,9; 245,69</t>
+          <t>-39,48; 223,62</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 124,44</t>
+          <t>-42,2; 110,85</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>1,38</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 7,32</t>
+          <t>-4,92; 6,96</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 7,01</t>
+          <t>-4,6; 8,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 4,97</t>
+          <t>-3,44; 5,57</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>13,56%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 104,12</t>
+          <t>-41,6; 102,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,84; 106,34</t>
+          <t>-34,92; 116,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 63,47</t>
+          <t>-28,92; 68,32</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-3,17</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>-2,88</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 2,47</t>
+          <t>-8,54; 2,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 1,94</t>
+          <t>-8,06; 2,12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 0,39</t>
+          <t>-7,07; 0,46</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-25,66%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>-25,87%</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>-25,66%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-57,71; 29,78</t>
+          <t>-55,45; 27,77</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-56,75; 22,17</t>
+          <t>-58,2; 24,72</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-50,48; 5,94</t>
+          <t>-50,64; 5,17</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,16</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>-1,49</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,01</t>
+          <t>-3,65; 1,17</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,13</t>
+          <t>-4,02; 1,06</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,44</t>
+          <t>-3,09; 0,63</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-12,97%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>-14,31%</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>-12,97%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 11,42</t>
+          <t>-35,43; 14,4</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 14,91</t>
+          <t>-34,82; 11,47</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 5,29</t>
+          <t>-29,15; 7,46</t>
         </is>
       </c>
     </row>
